--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>The option to stack up to ten accounts in parallel</t>
+          <t>Prime lets traders run up to ten funded accounts in parallel.</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Per-request payout cap, from $1,000 to $3,000 by account size</t>
+          <t>Per-request payout caps vary by programme and account size.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4850,7 +4850,7 @@
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>trustpilot_avis</t>
+          <t>trustpilot_review_count</t>
         </is>
       </c>
       <c r="B6" s="21" t="n"/>
@@ -4866,383 +4866,401 @@
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>marches</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>futures</t>
-        </is>
-      </c>
+          <t>trustpilot_url</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n"/>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>futures</t>
+          <t>https://www.trustpilot.com/review/exemple.com</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
+          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>titre</t>
+          <t>marches</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>Four routes to a funded futures account</t>
+          <t>futures</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>Four routes to a funded futures account</t>
+          <t>futures</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
+          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>titre</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase. Each program has its own loss limits, consistency rules and payout conditions.</t>
+          <t>Four routes to a funded futures account</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
+          <t>Four routes to a funded futures account</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
+          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite, Nitro and Prime settle at a 90% profit split; Instant pays 80%.</t>
+          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase. Each program has its own loss limits, consistency rules and payout conditions.</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
+          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
+          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite, Nitro and Prime settle at a 90% profit split; Instant pays 80%.</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
           <t>presentation</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>It suits futures traders who already have a method and want to choose the rule set that fits it, rather than accept one. Loss limits are dollar amounts rather than percentages, drawdown is calculated at the end of the day on the evaluation programs, and six platforms are selectable at purchase, including Tradovate, NinjaTrader and Quantower.
 The caveat matters more than the pricing. Quantum SRL holds no financial regulator licence, and every account is simulated: performance is hypothetical throughout. The live trading program exists but is a risk-team decision, not an entitlement earned at a fixed number of payouts.</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>annee_creation</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C12" s="24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>« Founded ». Vide : « — ».</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>pays</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
+          <t>annee_creation</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>2024</v>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>« Country ».</t>
+          <t>« Founded ». Vide : « — ».</t>
         </is>
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>ceo_fondateur</t>
+          <t>pays</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Christian Habibi</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Christian Habibi</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>« CEO / Founder ». Vide : « — ».</t>
+          <t>« Country ».</t>
         </is>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>actifs</t>
+          <t>ceo_fondateur</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+          <t>Christian Habibi</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+          <t>Christian Habibi</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
+          <t>« CEO / Founder ». Vide : « — ».</t>
         </is>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>categories_actifs</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n"/>
+          <t>actifs</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+        </is>
+      </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>(vide — non confirmees)</t>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
+          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>categories_actifs_statut</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>needs_confirmation</t>
-        </is>
-      </c>
+          <t>categories_actifs</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n"/>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>(vide — non confirmees)</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>plateformes</t>
+          <t>categories_actifs_statut</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
+          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>moyens_paiement</t>
+          <t>plateformes</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>Credit/Debit Card, Crypto</t>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Credit/Debit Card, Crypto</t>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
+          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>methodes_retrait</t>
+          <t>moyens_paiement</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Crypto, Riseworks</t>
+          <t>Credit/Debit Card, Crypto</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>Crypto, Riseworks</t>
+          <t>Credit/Debit Card, Crypto</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
+          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>prestataire_retrait</t>
+          <t>methodes_retrait</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>Rise</t>
+          <t>Crypto, Riseworks</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Rise</t>
+          <t>Crypto, Riseworks</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
+          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>levier</t>
+          <t>prestataire_retrait</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>N/A (futures contracts)</t>
+          <t>Rise</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>N/A (futures contracts)</t>
+          <t>Rise</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
+          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>levier_statut</t>
+          <t>levier</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>N/A (futures contracts)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>N/A (futures contracts)</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
+          <t>levier_statut</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
           <t>styles_trading</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>(vide — absent du releve)</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
         </is>
@@ -5250,10 +5268,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="B23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -2362,7 +2362,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>trading ou payouts : la carte ou la regle s'affiche.</t>
+          <t>trading, payouts, ou live (programme de compte reel, replie sous Payouts).</t>
         </is>
       </c>
       <c r="B2" s="25" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>Payment provider</t>
+          <t>Bank transfer</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>Rise. The first payout requires a Rise account and KYC.</t>
+          <t>1 to 3 days after approval.</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Bank transfer</t>
+          <t>Direct crypto</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>1 to 3 days after approval.</t>
+          <t>Maximum $500 per request. Above that, standard Rise methods apply.</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>Direct crypto</t>
+          <t>Elite maximum request</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>Maximum $500 per request. Above that, standard Rise methods apply.</t>
+          <t>Elite accounts bought from 2026-06-25 15:00 CET: 50% of total profit remaining, capped by account size. Older Elite accounts use 50% of current-cycle profit. Documented for Elite only.</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
@@ -3029,13 +3029,17 @@
           <t>confirmed</t>
         </is>
       </c>
-      <c r="E21" s="16" t="n"/>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
       <c r="F21" s="16" t="n"/>
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="inlineStr">
         <is>
-          <t>https://faq.futureselite.com/en/articles/11949985-how-are-payouts-processed</t>
+          <t>https://faq.futureselite.com/en/articles/16387630-how-much-can-i-request</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3051,12 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>Elite maximum request</t>
+          <t>What counts as a profitable day</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>Elite accounts bought from 2026-06-25 15:00 CET: 50% of total profit remaining, capped by account size. Older Elite accounts use 50% of current-cycle profit. Documented for Elite only.</t>
+          <t>Elite requires 6 profitable days per payout, and a day only qualifies above a size-specific minimum: $100 on a 25K, $150 on a 50K, $250 on a 100K, $350 on a 150K.</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
@@ -3070,39 +3074,47 @@
       <c r="H22" s="16" t="n"/>
       <c r="I22" s="16" t="inlineStr">
         <is>
-          <t>https://faq.futureselite.com/en/articles/16387630-how-much-can-i-request</t>
+          <t>https://futureselite.com/#pricing</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>payouts</t>
+          <t>trading</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>What counts as a profitable day</t>
+          <t>Prime 150K maximum loss</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>Elite requires 6 profitable days per payout, and a day only qualifies above a size-specific minimum: $100 on a 25K, $150 on a 50K, $250 on a 100K, $350 on a 150K.</t>
+          <t>Unresolved: the Prime overview and the live configurator show $4,500, while a detailed official MLL article has shown $4,000. The configurator value is used here.</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>source_conflict</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>elite</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="n"/>
+          <t>prime</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
       <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16" t="n"/>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
           <t>https://futureselite.com/#pricing</t>
@@ -3117,38 +3129,30 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>Prime 150K maximum loss</t>
+          <t>Instant 25K availability</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>Unresolved: the Prime overview and the live configurator show $4,500, while a detailed official MLL article has shown $4,000. The configurator value is used here.</t>
+          <t>Documented in the official Instant FAQ but not currently purchasable: the live configurator exposes only 50K, 100K and 150K.</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>source_conflict</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>prime</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>150000</t>
-        </is>
-      </c>
+          <t>instant</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="n"/>
       <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="H24" s="16" t="n"/>
       <c r="I24" s="16" t="inlineStr">
         <is>
-          <t>https://futureselite.com/#pricing</t>
+          <t>https://faq.futureselite.com/en/articles/12901358-how-do-payout-works-on-the-new-instant-challenges</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3164,12 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>Instant 25K availability</t>
+          <t>Prime evaluation length</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>Documented in the official Instant FAQ but not currently purchasable: the live configurator exposes only 50K, 100K and 150K.</t>
+          <t>Can be passed in one trading day. A separate FAQ article describes no minimum; the configurator states one day.</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
@@ -3175,71 +3179,71 @@
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>instant</t>
+          <t>prime</t>
         </is>
       </c>
       <c r="F25" s="16" t="n"/>
-      <c r="G25" s="16" t="n"/>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
       <c r="H25" s="16" t="n"/>
       <c r="I25" s="16" t="inlineStr">
         <is>
-          <t>https://faq.futureselite.com/en/articles/12901358-how-do-payout-works-on-the-new-instant-challenges</t>
+          <t>https://futureselite.com/#pricing</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>trading</t>
+          <t>live</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>Prime evaluation length</t>
+          <t>Transition to live</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>Can be passed in one trading day. A separate FAQ article describes no minimum; the configurator states one day.</t>
+          <t>A risk-team decision. The fifth payout is a ceiling, not an automatic entitlement.</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>prime</t>
-        </is>
-      </c>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="n"/>
       <c r="F26" s="16" t="n"/>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>funded</t>
         </is>
       </c>
       <c r="H26" s="16" t="n"/>
       <c r="I26" s="16" t="inlineStr">
         <is>
-          <t>https://futureselite.com/#pricing</t>
+          <t>https://faq.futureselite.com/en/articles/15899069-live-trading-program</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>payouts</t>
+          <t>live</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>Transition to live</t>
+          <t>Live starting balance</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>A risk-team decision. The fifth payout is a ceiling, not an automatic entitlement.</t>
+          <t>Starts at $0 with a loss floor based on account size. 50K example: $2,000 loss floor and $1,000 cushion.</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
@@ -3264,17 +3268,17 @@
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>payouts</t>
+          <t>live</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>Live starting balance</t>
+          <t>Live cushion unlock</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>Starts at $0 with a loss floor based on account size. 50K example: $2,000 loss floor and $1,000 cushion.</t>
+          <t>15 profitable days meeting the size-specific daily minimum. Days need not be consecutive.</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
@@ -3299,17 +3303,17 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>payouts</t>
+          <t>live</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>Live cushion unlock</t>
+          <t>Live payout</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>15 profitable days meeting the size-specific daily minimum. Days need not be consecutive.</t>
+          <t>Daily, $200 minimum, on profits above the cushion or unlocked reserve.</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
@@ -3334,17 +3338,17 @@
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>payouts</t>
+          <t>live</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>Live payout</t>
+          <t>Market data</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>Daily, $200 minimum, on profits above the cushion or unlocked reserve.</t>
+          <t>Exchange market data is the trader’s responsibility on a live account. Amount not specified.</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
@@ -3362,24 +3366,24 @@
       <c r="H30" s="16" t="n"/>
       <c r="I30" s="16" t="inlineStr">
         <is>
-          <t>https://faq.futureselite.com/en/articles/15899069-live-trading-program</t>
+          <t>https://faq.futureselite.com/en/articles/12291073-market-data-costs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>payouts</t>
+          <t>live</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>Market data</t>
+          <t>Commissions</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>Exchange market data is the trader’s responsibility on a live account. Amount not specified.</t>
+          <t>Commissions and exchange fees are charged per instrument on each executed trade. The official FAQ still labels some exchange fees as 2024 rates.</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
@@ -3397,24 +3401,24 @@
       <c r="H31" s="16" t="n"/>
       <c r="I31" s="16" t="inlineStr">
         <is>
-          <t>https://faq.futureselite.com/en/articles/12291073-market-data-costs</t>
+          <t>https://faq.futureselite.com/en/articles/12291021-what-are-the-costs-fees</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>payouts</t>
+          <t>live</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>Commissions</t>
+          <t>Platform licence</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>Commissions and exchange fees are charged per instrument on each executed trade. The official FAQ still labels some exchange fees as 2024 rates.</t>
+          <t>A paid platform licence may apply depending on the selected platform.</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
@@ -3439,17 +3443,17 @@
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>payouts</t>
+          <t>live</t>
         </is>
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>Platform licence</t>
+          <t>Maintenance fee</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>A paid platform licence may apply depending on the selected platform.</t>
+          <t>No hidden administrative maintenance fee is stated: $0.</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
@@ -3472,39 +3476,15 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>payouts</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>Maintenance fee</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>No hidden administrative maintenance fee is stated: $0.</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
+      <c r="A34" s="16" t="n"/>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
       <c r="E34" s="16" t="n"/>
       <c r="F34" s="16" t="n"/>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>funded</t>
-        </is>
-      </c>
+      <c r="G34" s="16" t="n"/>
       <c r="H34" s="16" t="n"/>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>https://faq.futureselite.com/en/articles/12291021-what-are-the-costs-fees</t>
-        </is>
-      </c>
+      <c r="I34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="n"/>
@@ -3839,7 +3819,7 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A3:A64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$P$2:$P$3</formula1>
+      <formula1>=Listes!$P$2:$P$4</formula1>
     </dataValidation>
     <dataValidation sqref="D3:D64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$A$2:$A$6</formula1>
@@ -4690,6 +4670,11 @@
       <c r="O4" s="11" t="inlineStr">
         <is>
           <t>limite</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
       <c r="Q4" s="11" t="inlineStr">

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -2298,7 +2298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2309,7 +2309,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2355,6 +2356,11 @@
       </c>
       <c r="I1" s="14" t="inlineStr">
         <is>
+          <t>essentielle</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
           <t>source_url</t>
         </is>
       </c>
@@ -2401,6 +2407,11 @@
         </is>
       </c>
       <c r="I2" s="25" t="inlineStr">
+        <is>
+          <t>oui : affichee sur la page. Les autres restent dans le tableur sans s'afficher. Quatre par carte au plus.</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="inlineStr">
         <is>
           <t>Page officielle. Non affichee.</t>
         </is>
@@ -2433,6 +2444,11 @@
       <c r="H3" s="16" t="n"/>
       <c r="I3" s="16" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
           <t>https://faq.futureselite.com/en/articles/11949421-futures-trading-hours-and-guidelines</t>
         </is>
       </c>
@@ -2468,6 +2484,11 @@
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
           <t>https://faq.futureselite.com/en/articles/11949421-futures-trading-hours-and-guidelines</t>
         </is>
       </c>
@@ -2497,7 +2518,8 @@
       <c r="F5" s="16" t="n"/>
       <c r="G5" s="16" t="n"/>
       <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/11949421-futures-trading-hours-and-guidelines</t>
         </is>
@@ -2534,6 +2556,11 @@
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
           <t>https://faq.futureselite.com/en/articles/11949446-what-is-allowed-and-not-allowed-with-us-fair-play-and-prohibited-trading-practices</t>
         </is>
       </c>
@@ -2567,7 +2594,8 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/11949446-what-is-allowed-and-not-allowed-with-us-fair-play-and-prohibited-trading-practices</t>
         </is>
@@ -2602,7 +2630,8 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/11949446-what-is-allowed-and-not-allowed-with-us-fair-play-and-prohibited-trading-practices</t>
         </is>
@@ -2637,7 +2666,8 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/11949446-what-is-allowed-and-not-allowed-with-us-fair-play-and-prohibited-trading-practices</t>
         </is>
@@ -2668,7 +2698,8 @@
       <c r="F10" s="16" t="n"/>
       <c r="G10" s="16" t="n"/>
       <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>https://futureselite.com/#pricing</t>
         </is>
@@ -2708,6 +2739,11 @@
       </c>
       <c r="H11" s="16" t="n"/>
       <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>https://futureselite.com/#pricing</t>
         </is>
@@ -2742,7 +2778,8 @@
         </is>
       </c>
       <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>https://futureselite.com/#pricing</t>
         </is>
@@ -2775,6 +2812,11 @@
       <c r="H13" s="16" t="n"/>
       <c r="I13" s="16" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
           <t>https://faq.futureselite.com/en/articles/11948842-know-your-customer-kyc-policy</t>
         </is>
       </c>
@@ -2808,7 +2850,8 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/12291084-trader-rules-responsibilities</t>
         </is>
@@ -2839,7 +2882,8 @@
       <c r="F15" s="16" t="n"/>
       <c r="G15" s="16" t="n"/>
       <c r="H15" s="16" t="n"/>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/12291084-trader-rules-responsibilities</t>
         </is>
@@ -2878,7 +2922,8 @@
         </is>
       </c>
       <c r="H16" s="16" t="n"/>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/16778908-is-the-challenge-fee-is-one-time</t>
         </is>
@@ -2897,7 +2942,7 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Maximum 10 funded accounts overall; maximum 10 Prime; maximum 5 combined across Elite, Custom, Instant and Nitro. Nitro funded-account limit: not confirmed.</t>
+          <t>Maximum 10 funded accounts overall; maximum 10 Prime; maximum 5 combined across Elite, Custom, Instant and Nitro.</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
@@ -2909,7 +2954,8 @@
       <c r="F17" s="16" t="n"/>
       <c r="G17" s="16" t="n"/>
       <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/11949051-how-many-accounts-can-i-have-with-futureselite</t>
         </is>
@@ -2942,6 +2988,11 @@
       <c r="H18" s="16" t="n"/>
       <c r="I18" s="16" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
           <t>https://faq.futureselite.com/en/articles/11949982-what-is-the-payout-process-like-on-futures-elite</t>
         </is>
       </c>
@@ -2973,6 +3024,11 @@
       <c r="H19" s="16" t="n"/>
       <c r="I19" s="16" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
           <t>https://faq.futureselite.com/en/articles/11949985-how-are-payouts-processed</t>
         </is>
       </c>
@@ -3002,7 +3058,8 @@
       <c r="F20" s="16" t="n"/>
       <c r="G20" s="16" t="n"/>
       <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/11949985-how-are-payouts-processed</t>
         </is>
@@ -3037,7 +3094,8 @@
       <c r="F21" s="16" t="n"/>
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="16" t="n"/>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/16387630-how-much-can-i-request</t>
         </is>
@@ -3074,6 +3132,11 @@
       <c r="H22" s="16" t="n"/>
       <c r="I22" s="16" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
           <t>https://futureselite.com/#pricing</t>
         </is>
       </c>
@@ -3115,7 +3178,8 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>https://futureselite.com/#pricing</t>
         </is>
@@ -3150,7 +3214,8 @@
       <c r="F24" s="16" t="n"/>
       <c r="G24" s="16" t="n"/>
       <c r="H24" s="16" t="n"/>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I24" s="16" t="n"/>
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/12901358-how-do-payout-works-on-the-new-instant-challenges</t>
         </is>
@@ -3189,7 +3254,8 @@
         </is>
       </c>
       <c r="H25" s="16" t="n"/>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I25" s="16" t="n"/>
+      <c r="J25" s="16" t="inlineStr">
         <is>
           <t>https://futureselite.com/#pricing</t>
         </is>
@@ -3226,6 +3292,11 @@
       <c r="H26" s="16" t="n"/>
       <c r="I26" s="16" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
           <t>https://faq.futureselite.com/en/articles/15899069-live-trading-program</t>
         </is>
       </c>
@@ -3259,7 +3330,8 @@
         </is>
       </c>
       <c r="H27" s="16" t="n"/>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/15899069-live-trading-program</t>
         </is>
@@ -3294,7 +3366,8 @@
         </is>
       </c>
       <c r="H28" s="16" t="n"/>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/15899069-live-trading-program</t>
         </is>
@@ -3329,7 +3402,8 @@
         </is>
       </c>
       <c r="H29" s="16" t="n"/>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="I29" s="16" t="n"/>
+      <c r="J29" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/15899069-live-trading-program</t>
         </is>
@@ -3364,7 +3438,8 @@
         </is>
       </c>
       <c r="H30" s="16" t="n"/>
-      <c r="I30" s="16" t="inlineStr">
+      <c r="I30" s="16" t="n"/>
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/12291073-market-data-costs</t>
         </is>
@@ -3399,7 +3474,8 @@
         </is>
       </c>
       <c r="H31" s="16" t="n"/>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="I31" s="16" t="n"/>
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/12291021-what-are-the-costs-fees</t>
         </is>
@@ -3434,7 +3510,8 @@
         </is>
       </c>
       <c r="H32" s="16" t="n"/>
-      <c r="I32" s="16" t="inlineStr">
+      <c r="I32" s="16" t="n"/>
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/12291021-what-are-the-costs-fees</t>
         </is>
@@ -3469,7 +3546,8 @@
         </is>
       </c>
       <c r="H33" s="16" t="n"/>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="I33" s="16" t="n"/>
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>https://faq.futureselite.com/en/articles/12291021-what-are-the-costs-fees</t>
         </is>
@@ -3485,6 +3563,7 @@
       <c r="G34" s="16" t="n"/>
       <c r="H34" s="16" t="n"/>
       <c r="I34" s="16" t="n"/>
+      <c r="J34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="n"/>
@@ -3496,6 +3575,7 @@
       <c r="G35" s="16" t="n"/>
       <c r="H35" s="16" t="n"/>
       <c r="I35" s="16" t="n"/>
+      <c r="J35" s="16" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="n"/>
@@ -3507,6 +3587,7 @@
       <c r="G36" s="16" t="n"/>
       <c r="H36" s="16" t="n"/>
       <c r="I36" s="16" t="n"/>
+      <c r="J36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="n"/>
@@ -3518,6 +3599,7 @@
       <c r="G37" s="16" t="n"/>
       <c r="H37" s="16" t="n"/>
       <c r="I37" s="16" t="n"/>
+      <c r="J37" s="16" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="n"/>
@@ -3529,6 +3611,7 @@
       <c r="G38" s="16" t="n"/>
       <c r="H38" s="16" t="n"/>
       <c r="I38" s="16" t="n"/>
+      <c r="J38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="n"/>
@@ -3540,6 +3623,7 @@
       <c r="G39" s="16" t="n"/>
       <c r="H39" s="16" t="n"/>
       <c r="I39" s="16" t="n"/>
+      <c r="J39" s="16" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="n"/>
@@ -3551,6 +3635,7 @@
       <c r="G40" s="16" t="n"/>
       <c r="H40" s="16" t="n"/>
       <c r="I40" s="16" t="n"/>
+      <c r="J40" s="16" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="n"/>
@@ -3562,6 +3647,7 @@
       <c r="G41" s="16" t="n"/>
       <c r="H41" s="16" t="n"/>
       <c r="I41" s="16" t="n"/>
+      <c r="J41" s="16" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="n"/>
@@ -3573,6 +3659,7 @@
       <c r="G42" s="16" t="n"/>
       <c r="H42" s="16" t="n"/>
       <c r="I42" s="16" t="n"/>
+      <c r="J42" s="16" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="n"/>
@@ -3584,6 +3671,7 @@
       <c r="G43" s="16" t="n"/>
       <c r="H43" s="16" t="n"/>
       <c r="I43" s="16" t="n"/>
+      <c r="J43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="n"/>
@@ -3595,6 +3683,7 @@
       <c r="G44" s="16" t="n"/>
       <c r="H44" s="16" t="n"/>
       <c r="I44" s="16" t="n"/>
+      <c r="J44" s="16" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="n"/>
@@ -3606,6 +3695,7 @@
       <c r="G45" s="16" t="n"/>
       <c r="H45" s="16" t="n"/>
       <c r="I45" s="16" t="n"/>
+      <c r="J45" s="16" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="n"/>
@@ -3617,6 +3707,7 @@
       <c r="G46" s="16" t="n"/>
       <c r="H46" s="16" t="n"/>
       <c r="I46" s="16" t="n"/>
+      <c r="J46" s="16" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="n"/>
@@ -3628,6 +3719,7 @@
       <c r="G47" s="16" t="n"/>
       <c r="H47" s="16" t="n"/>
       <c r="I47" s="16" t="n"/>
+      <c r="J47" s="16" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="n"/>
@@ -3639,6 +3731,7 @@
       <c r="G48" s="16" t="n"/>
       <c r="H48" s="16" t="n"/>
       <c r="I48" s="16" t="n"/>
+      <c r="J48" s="16" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="n"/>
@@ -3650,6 +3743,7 @@
       <c r="G49" s="16" t="n"/>
       <c r="H49" s="16" t="n"/>
       <c r="I49" s="16" t="n"/>
+      <c r="J49" s="16" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="n"/>
@@ -3661,6 +3755,7 @@
       <c r="G50" s="16" t="n"/>
       <c r="H50" s="16" t="n"/>
       <c r="I50" s="16" t="n"/>
+      <c r="J50" s="16" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="n"/>
@@ -3672,6 +3767,7 @@
       <c r="G51" s="16" t="n"/>
       <c r="H51" s="16" t="n"/>
       <c r="I51" s="16" t="n"/>
+      <c r="J51" s="16" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="n"/>
@@ -3683,6 +3779,7 @@
       <c r="G52" s="16" t="n"/>
       <c r="H52" s="16" t="n"/>
       <c r="I52" s="16" t="n"/>
+      <c r="J52" s="16" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="n"/>
@@ -3694,6 +3791,7 @@
       <c r="G53" s="16" t="n"/>
       <c r="H53" s="16" t="n"/>
       <c r="I53" s="16" t="n"/>
+      <c r="J53" s="16" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="n"/>
@@ -3705,6 +3803,7 @@
       <c r="G54" s="16" t="n"/>
       <c r="H54" s="16" t="n"/>
       <c r="I54" s="16" t="n"/>
+      <c r="J54" s="16" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="n"/>
@@ -3716,6 +3815,7 @@
       <c r="G55" s="16" t="n"/>
       <c r="H55" s="16" t="n"/>
       <c r="I55" s="16" t="n"/>
+      <c r="J55" s="16" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="n"/>
@@ -3727,6 +3827,7 @@
       <c r="G56" s="16" t="n"/>
       <c r="H56" s="16" t="n"/>
       <c r="I56" s="16" t="n"/>
+      <c r="J56" s="16" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="n"/>
@@ -3738,6 +3839,7 @@
       <c r="G57" s="16" t="n"/>
       <c r="H57" s="16" t="n"/>
       <c r="I57" s="16" t="n"/>
+      <c r="J57" s="16" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="n"/>
@@ -3749,6 +3851,7 @@
       <c r="G58" s="16" t="n"/>
       <c r="H58" s="16" t="n"/>
       <c r="I58" s="16" t="n"/>
+      <c r="J58" s="16" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="n"/>
@@ -3760,6 +3863,7 @@
       <c r="G59" s="16" t="n"/>
       <c r="H59" s="16" t="n"/>
       <c r="I59" s="16" t="n"/>
+      <c r="J59" s="16" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="n"/>
@@ -3771,6 +3875,7 @@
       <c r="G60" s="16" t="n"/>
       <c r="H60" s="16" t="n"/>
       <c r="I60" s="16" t="n"/>
+      <c r="J60" s="16" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="n"/>
@@ -3782,6 +3887,7 @@
       <c r="G61" s="16" t="n"/>
       <c r="H61" s="16" t="n"/>
       <c r="I61" s="16" t="n"/>
+      <c r="J61" s="16" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="n"/>
@@ -3793,6 +3899,7 @@
       <c r="G62" s="16" t="n"/>
       <c r="H62" s="16" t="n"/>
       <c r="I62" s="16" t="n"/>
+      <c r="J62" s="16" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="n"/>
@@ -3804,6 +3911,7 @@
       <c r="G63" s="16" t="n"/>
       <c r="H63" s="16" t="n"/>
       <c r="I63" s="16" t="n"/>
+      <c r="J63" s="16" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="n"/>
@@ -3815,9 +3923,10 @@
       <c r="G64" s="16" t="n"/>
       <c r="H64" s="16" t="n"/>
       <c r="I64" s="16" t="n"/>
+      <c r="J64" s="16" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="A3:A64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$P$2:$P$4</formula1>
     </dataValidation>
@@ -3828,6 +3937,9 @@
       <formula1>=Listes!$Q$2:$Q$4</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$N$2:$N$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="I3:I64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$N$2:$N$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>The configurator displays "Yes".</t>
+          <t>Allowed during the evaluation.</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -4934,7 +4934,9 @@
           <t>trustpilot_score</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n"/>
+      <c r="B5" s="19" t="n">
+        <v>4.7</v>
+      </c>
       <c r="C5" s="20" t="n">
         <v>4.5</v>
       </c>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>One phase on Elite, Nitro and Prime: reach the profit objective without breaching the maximum loss. There is no deadline to pass. Minimum trading days differ by programme, and Instant has no evaluation at all.</t>
+          <t>One phase on Elite, Nitro and Prime: reach the profit objective without breaching the maximum loss. There is no deadline to pass. Minimum trading days differ by program, and Instant has no evaluation at all.</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>The simulated funded account opens with no activation fee. Drawdown type and contract scaling change with the programme, so the rules table above is the one that applies.</t>
+          <t>The simulated funded account opens with no activation fee. Drawdown type and contract scaling change with the program, so the rules table above is the one that applies.</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Per-request payout caps vary by programme and account size.</t>
+          <t>Per-request payout caps vary by program and account size.</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
-          <t>The only programme with a daily loss limit in both phases. It also carries the longest bundle ladder, up to ten accounts.</t>
+          <t>The only program with a daily loss limit in both phases. It also carries the longest bundle ladder, up to ten accounts.</t>
         </is>
       </c>
       <c r="H5" s="23" t="n">

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1483,13 +1483,38 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>needs_confirmation</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>needs_confirmation</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Seule une offre confirmed s'affiche : remise, code, Copy code et Claim deal. Vide ou needs_confirmation : la carte garde le plan, le prix public et Continue to.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$N$2:$N$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"confirmed,needs_confirmation"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4968,7 +4993,11 @@
           <t>trustpilot_url</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>https://www.trustpilot.com/review/futureselite.com</t>
+        </is>
+      </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/exemple.com</t>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -4856,7 +4856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5391,6 +5391,20 @@
       <c r="D25" s="18" t="inlineStr">
         <is>
           <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>meta_description</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O404"/>
+  <dimension ref="A1:Q404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10049,6 +10063,8 @@
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -10127,6 +10143,16 @@
           <t>controle  (auto)</t>
         </is>
       </c>
+      <c r="P1" s="14" t="inlineStr">
+        <is>
+          <t>partage_bas</t>
+        </is>
+      </c>
+      <c r="Q1" s="14" t="inlineStr">
+        <is>
+          <t>seuil_partage</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -10202,6 +10228,16 @@
       <c r="O2" s="25" t="inlineStr">
         <is>
           <t>ok, ou plan introuvable.</t>
+        </is>
+      </c>
+      <c r="P2" s="25" t="inlineStr">
+        <is>
+          <t>Partage par palier : le taux SOUS le seuil (50 %). Vide si un seul taux. Le taux au-dessus va dans « partage ».</t>
+        </is>
+      </c>
+      <c r="Q2" s="25" t="inlineStr">
+        <is>
+          <t>Montant d'une demande de retrait a partir duquel « partage » s'applique. En devise. Avec partage_bas.</t>
         </is>
       </c>
     </row>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -4480,7 +4480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4826,6 +4826,11 @@
           <t>needs_confirmation</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>certification</t>
+        </is>
+      </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
           <t>crypto</t>
@@ -4844,6 +4849,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5678,12 +5684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5702,6 +5709,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -5717,6 +5729,11 @@
       <c r="C2" s="25" t="inlineStr">
         <is>
           <t>Pourquoi, d'ou vient le nom. Non affiche.</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>Icone officielle, prise sur le site de l'editeur (https). Vide : pastille a l'initiale.</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L153"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6574,6 +6591,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6637,6 +6655,11 @@
           <t>controle  (auto)</t>
         </is>
       </c>
+      <c r="M1" s="14" t="inlineStr">
+        <is>
+          <t>lien_plan</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -6697,6 +6720,11 @@
       <c r="L2" s="25" t="inlineStr">
         <is>
           <t>ok, ou ce qui manque.</t>
+        </is>
+      </c>
+      <c r="M2" s="25" t="inlineStr">
+        <is>
+          <t>Slug du plan dans prop_firm_challenges (voir DIAGNOSTIC-liens-plans). Les boutons ouvrent alors son lien profond : paiement de CE plan, code applique. Vide : lien general de la firme.</t>
         </is>
       </c>
     </row>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -4480,7 +4480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4849,7 +4849,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4862,7 +4861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5411,6 +5410,20 @@
       <c r="D26" s="18" t="inlineStr">
         <is>
           <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>flux_donnees</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
         </is>
       </c>
     </row>
@@ -19160,7 +19173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19169,6 +19182,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -19202,6 +19216,11 @@
           <t>programmes</t>
         </is>
       </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -19232,6 +19251,11 @@
       <c r="F2" s="25" t="inlineStr">
         <is>
           <t>Slugs concernes, separes par des virgules. Vide : tous les programmes.</t>
+        </is>
+      </c>
+      <c r="G2" s="25" t="inlineStr">
+        <is>
+          <t>Icone officielle de l'option, prise sur le site de l'editeur (https). Vide : logo de la plateforme du meme nom, sinon initiale.</t>
         </is>
       </c>
     </row>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B3" s="31" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C3" s="30" t="n">
         <v>0.3</v>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -6589,7 +6589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:N153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6605,6 +6605,7 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6673,6 +6674,11 @@
           <t>lien_plan</t>
         </is>
       </c>
+      <c r="N1" s="14" t="inlineStr">
+        <is>
+          <t>devise_compte</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -6738,6 +6744,11 @@
       <c r="M2" s="25" t="inlineStr">
         <is>
           <t>Slug du plan dans prop_firm_challenges (voir DIAGNOSTIC-liens-plans). Les boutons ouvrent alors son lien profond : paiement de CE plan, code applique. Vide : lien general de la firme.</t>
+        </is>
+      </c>
+      <c r="N2" s="25" t="inlineStr">
+        <is>
+          <t>Devise du SOLDE du compte : la taille, l'objectif et les limites. Vide : la devise du prix. A remplir quand la firme facture dans une monnaie et libelle les comptes dans une autre.</t>
         </is>
       </c>
     </row>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -5762,6 +5762,11 @@
         </is>
       </c>
       <c r="C3" s="16" t="n"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://trader.tradovate.com/img/icons/iphone-retina.png</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -5779,6 +5784,11 @@
           <t>Potential external licence cost in live trading.</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://ninjatrader.com/assets/dist/images/favicons/apple-touch-icon.png</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -5792,6 +5802,11 @@
         </is>
       </c>
       <c r="C5" s="16" t="n"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.quantower.com/favicon.ico</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -5805,6 +5820,11 @@
         </is>
       </c>
       <c r="C6" s="16" t="n"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://atas.net/wp-content/uploads/2026/01/atas_icon-300x300.png</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -5818,6 +5838,11 @@
         </is>
       </c>
       <c r="C7" s="16" t="n"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.wealthcharts.com/favicon.ico</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -5833,6 +5858,11 @@
       <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Written DeepChart in the purchase configurator and DeepCharts® on the official homepage; one product. The dashboard provides credentials and a Dxfeed agreement flow.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://framerusercontent.com/images/AoZRfVkVLzahOuchkWO16EoZOo.png</t>
         </is>
       </c>
     </row>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -2323,7 +2323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2389,6 +2389,11 @@
           <t>source_url</t>
         </is>
       </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>variantes</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -2439,6 +2444,11 @@
       <c r="J2" s="25" t="inlineStr">
         <is>
           <t>Page officielle. Non affichee.</t>
+        </is>
+      </c>
+      <c r="K2" s="25" t="inlineStr">
+        <is>
+          <t>Variantes concernees (Day Trade, Swing, NEW...), separees par des virgules. Vide : toutes.</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6048,6 +6058,16 @@
           <t>nb_plans  (auto)</t>
         </is>
       </c>
+      <c r="L1" s="14" t="inlineStr">
+        <is>
+          <t>offre_fin</t>
+        </is>
+      </c>
+      <c r="M1" s="14" t="inlineStr">
+        <is>
+          <t>offre_fin_statut</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -6103,6 +6123,16 @@
       <c r="K2" s="25" t="inlineStr">
         <is>
           <t>Plans rattaches.</t>
+        </is>
+      </c>
+      <c r="L2" s="25" t="inlineStr">
+        <is>
+          <t>Campagne a duree limitee : sa date de fin. Vide si le programme est permanent.</t>
+        </is>
+      </c>
+      <c r="M2" s="25" t="inlineStr">
+        <is>
+          <t>confirmed si la date est publiee. Sinon not_published, needs_confirmation ou source_conflict.</t>
         </is>
       </c>
     </row>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1502,6 +1502,18 @@
       <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Seule une offre confirmed s'affiche : remise, code, Copy code et Claim deal. Vide ou needs_confirmation : la carte garde le plan, le prix public et Continue to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>accroche</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
         </is>
       </c>
     </row>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1514,6 +1514,30 @@
       <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>remise_campagne</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Taux d'une campagne a duree limitee, en %. Il remplace « remise » jusqu'a « campagne_fin », puis la fiche revient a « remise ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>campagne_fin</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
         </is>
       </c>
     </row>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1538,6 +1538,18 @@
       <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>bonus</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Deux ou trois mots pour ce que l'offre donne en plus du pourcentage (« +1 free reset »). Affiche en pastille sur la fiche et sur la carte /compare. Suit la campagne : il disparait avec elle.</t>
         </is>
       </c>
     </row>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -17,15 +17,16 @@
     <sheet name="Phases" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="OptionsAchat" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Offre" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Conditions" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Parcours" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Formation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ComptesApresReussite" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Couts" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Regles" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Verdict" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="FAQ" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Listes" sheetId="19" state="hidden" r:id="rId19"/>
+    <sheet name="Campagnes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Conditions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Parcours" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Formation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ComptesApresReussite" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Couts" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Regles" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Verdict" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="FAQ" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Listes" sheetId="20" state="hidden" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1573,6 +1574,92 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>debut</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>remise</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Date et heure ISO d'ouverture. Avant elle, la campagne n'existe nulle part.</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>Date et heure ISO de fermeture. Passee, la campagne disparait d'elle-meme.</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
+        <is>
+          <t>Deux ou trois mots, pour la pastille : « Day 4 · -60% TCP25 ».</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>Une phrase : ce que l'offre donne, telle qu'elle s'affiche.</t>
+        </is>
+      </c>
+      <c r="E2" s="25" t="inlineStr">
+        <is>
+          <t>Taux pendant la fenetre, en %. Vide : le taux habituel de l'offre ne change pas.</t>
+        </is>
+      </c>
+      <c r="F2" s="25" t="inlineStr">
+        <is>
+          <t>confirmed pour s'afficher. Toute autre valeur la garde en reserve.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="004B5563"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1680,7 +1767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -1883,7 +1970,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -1993,7 +2080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -2182,7 +2269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -2364,7 +2451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -4031,7 +4118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -4346,7 +4433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -4531,7 +4618,594 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F2937"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Champ</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Valeur a remplir</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Exemple — FuturesElite, 7 sept. 2026</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Ou ca s'affiche dans le HTML · si vide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>futureselite</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>futureselite</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>N'est pas affiche : sert a l'adresse de la page et au lien sortant. Minuscules, sans espace. Obligatoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>FuturesElite</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>Le titre de la carte d'identite, « Continue to [Firm] », le verdict et la FAQ. Obligatoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>https://cdn.prod.website-files.com/690a53b4dc85f8bf1d3328d4/690a53b4dc85f8bf1d332987_Webclip.svg</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>https://www.google.com/s2/favicons?domain=futureselite.com&amp;sz=128</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Le logo, en tuile blanche. Il n'est pas cliquable : les sorties passent par Claim deal et Continue to. Vide : initiale du nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_score</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Hero, angle haut droit : note sur 5. Vide : le bloc Trustpilot n'apparait pas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_review_count</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n"/>
+      <c r="C6" s="22" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Nombre d'avis sous la note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_url</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>https://www.trustpilot.com/review/futureselite.com</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>https://www.trustpilot.com/review/exemple.com</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>marches</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>futures</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>futures</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Four routes to a funded futures account</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Four routes to a funded futures account</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase. Each program has its own loss limits, consistency rules and payout conditions.</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite, Nitro and Prime settle at a 90% profit split; Instant pays 80%.</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>presentation</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>It suits futures traders who already have a method and want to choose the rule set that fits it, rather than accept one. Loss limits are dollar amounts rather than percentages, drawdown is calculated at the end of the day on the evaluation programs, and six platforms are selectable at purchase, including Tradovate, NinjaTrader and Quantower.
+The caveat matters more than the pricing. Quantum SRL holds no financial regulator licence, and every account is simulated: performance is hypothetical throughout. The live trading program exists but is a risk-team decision, not an entitlement earned at a fixed number of payouts.</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>annee_creation</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>« Founded ». Vide : « — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>pays</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>« Country ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>ceo_fondateur</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Christian Habibi</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Christian Habibi</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>« CEO / Founder ». Vide : « — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>actifs</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>categories_actifs</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>(vide — non confirmees)</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>categories_actifs_statut</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>needs_confirmation</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>needs_confirmation</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>plateformes</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>moyens_paiement</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Credit/Debit Card, Crypto</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Credit/Debit Card, Crypto</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>methodes_retrait</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Crypto, Riseworks</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Crypto, Riseworks</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>prestataire_retrait</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Rise</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Rise</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>levier</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>N/A (futures contracts)</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>N/A (futures contracts)</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>levier_statut</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>styles_trading</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>(vide — absent du releve)</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>meta_description</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>flux_donnees</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009CA3AF"/>
@@ -4909,593 +5583,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F2937"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Champ</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Valeur a remplir</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Exemple — FuturesElite, 7 sept. 2026</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Ou ca s'affiche dans le HTML · si vide</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>slug</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>futureselite</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>futureselite</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>N'est pas affiche : sert a l'adresse de la page et au lien sortant. Minuscules, sans espace. Obligatoire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>nom</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>FuturesElite</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>FuturesElite</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>Le titre de la carte d'identite, « Continue to [Firm] », le verdict et la FAQ. Obligatoire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>logo_url</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>https://cdn.prod.website-files.com/690a53b4dc85f8bf1d3328d4/690a53b4dc85f8bf1d332987_Webclip.svg</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>https://www.google.com/s2/favicons?domain=futureselite.com&amp;sz=128</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>Le logo, en tuile blanche. Il n'est pas cliquable : les sorties passent par Claim deal et Continue to. Vide : initiale du nom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_score</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="C5" s="20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>Hero, angle haut droit : note sur 5. Vide : le bloc Trustpilot n'apparait pas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_review_count</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n"/>
-      <c r="C6" s="22" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>Nombre d'avis sous la note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_url</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>https://www.trustpilot.com/review/futureselite.com</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>https://www.trustpilot.com/review/exemple.com</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>marches</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>futures</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>futures</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>titre</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Four routes to a funded futures account</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Four routes to a funded futures account</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase. Each program has its own loss limits, consistency rules and payout conditions.</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>resume</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite, Nitro and Prime settle at a 90% profit split; Instant pays 80%.</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>presentation</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>It suits futures traders who already have a method and want to choose the rule set that fits it, rather than accept one. Loss limits are dollar amounts rather than percentages, drawdown is calculated at the end of the day on the evaluation programs, and six platforms are selectable at purchase, including Tradovate, NinjaTrader and Quantower.
-The caveat matters more than the pricing. Quantum SRL holds no financial regulator licence, and every account is simulated: performance is hypothetical throughout. The live trading program exists but is a risk-team decision, not an entitlement earned at a fixed number of payouts.</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>annee_creation</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C13" s="24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>« Founded ». Vide : « — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>pays</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>« Country ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>ceo_fondateur</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>Christian Habibi</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Christian Habibi</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>« CEO / Founder ». Vide : « — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>actifs</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>categories_actifs</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>(vide — non confirmees)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>categories_actifs_statut</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>needs_confirmation</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>needs_confirmation</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>plateformes</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>moyens_paiement</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Credit/Debit Card, Crypto</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Credit/Debit Card, Crypto</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>methodes_retrait</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Crypto, Riseworks</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Crypto, Riseworks</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>prestataire_retrait</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>Rise</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Rise</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>levier</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>N/A (futures contracts)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>N/A (futures contracts)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>levier_statut</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>styles_trading</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>(vide — absent du releve)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>meta_description</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>flux_donnees</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$6</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
